--- a/SIM Slot List 202507.xlsx
+++ b/SIM Slot List 202507.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75A7D66-E2D6-6F46-9A11-08F3849BD00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1762C12-FF6F-1A4E-8D36-7176CA1A459F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17160" yWindow="1020" windowWidth="16880" windowHeight="21080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,20 @@
   <definedNames>
     <definedName name="JR_PAGE_ANCHOR_0_1">'SIM Slot List'!$A$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2568,7 +2581,7 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1">
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -2628,7 +2641,7 @@
       </c>
       <c r="T3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="38" customHeight="1">
+    <row r="4" spans="1:20" ht="30" customHeight="1" thickBot="1">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -2672,7 +2685,7 @@
       </c>
       <c r="T4" s="3"/>
     </row>
-    <row r="5" spans="1:20" ht="38" customHeight="1">
+    <row r="5" spans="1:20" ht="38" customHeight="1" thickBot="1">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
